--- a/upload/legislacao.xlsx
+++ b/upload/legislacao.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CCBA998-B407-4AD7-A388-01AF68D25FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{8B7AD714-638F-4DF5-AD50-A23C076DBBC9}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$1</definedName>
+  </definedNames>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="147">
   <si>
     <t>TEMA</t>
   </si>
@@ -47,15 +49,6 @@
     <t>LINK</t>
   </si>
   <si>
-    <t>Pesquisa Legislativa</t>
-  </si>
-  <si>
-    <t>Consulte as Leis e Decretos, bem como seus regulamentos (resoluções, portarias ...) de todos os órgãos do poder executivo de Minas Gerais. </t>
-  </si>
-  <si>
-    <t>https://www.almg.gov.br/atividade-parlamentar/leis/legislacao-mineira/</t>
-  </si>
-  <si>
     <t>Constituição da República Federativa do Brasil de 1988 </t>
   </si>
   <si>
@@ -68,9 +61,6 @@
     <t>https://www.planalto.gov.br/ccivil_03/leis/LCP/Lcp131.htm</t>
   </si>
   <si>
-    <t>https://www.planalto.gov.br/ccivil_03/_ato2007-2010/2010/decreto/d7185.htm</t>
-  </si>
-  <si>
     <t>https://www.planalto.gov.br/ccivil_03/_ato2011-2014/2011/lei/l12527.htm</t>
   </si>
   <si>
@@ -83,9 +73,6 @@
     <t>Regulamenta o direito constitucional de acesso dos cidadãos às informações públicas e é aplicável aos três Poderes da União, dos Estados, do Distrito Federal e dos Municípios. </t>
   </si>
   <si>
-    <t>Dispõe sobre o padrão mínimo de qualidade do sistema integrado de administração financeira e controle, no âmbito de cada ente da Federação, nos termos do art. 48, parágrafo único, inciso III, da Lei Complementar no 101, de 4 de maio de 2000, e dá outras providências. </t>
-  </si>
-  <si>
     <t>Acrescenta dispositivos à Lei Complementar nº 101, de 4 de maio de 2000, que estabelece normas de finanças públicas voltadas para a responsabilidade na gestão fiscal e dá outras providências, a fim de determinar a disponibilização, em tempo real, de informações pormenorizadas sobre a execução. </t>
   </si>
   <si>
@@ -98,9 +85,6 @@
     <t>Lei Complementar nº 131, de 27 de Maio de 2009 </t>
   </si>
   <si>
-    <t>Decreto Federal nº 7.185, de 27 de Maio de 2010 </t>
-  </si>
-  <si>
     <t>Lei Federal nº 12.527, de 18 de novembro de 2011 </t>
   </si>
   <si>
@@ -113,18 +97,12 @@
     <t>CONSTITUIÇÃO DA REPÚBLICA </t>
   </si>
   <si>
-    <t>PESQUISA LEGISLATIVA </t>
-  </si>
-  <si>
     <t>PROTEÇÃO DE DADOS PESSOAIS </t>
   </si>
   <si>
     <t>Lei Federal nº 13.709, de 14 de agosto de 2018 </t>
   </si>
   <si>
-    <t>Decreto Estadual nº 48.237 de 22/07/2021</t>
-  </si>
-  <si>
     <t>Dispõe sobre a aplicação da Lei Federal nº 13.709, de 14 de agosto de 2018, Lei Geral de Proteção de Dados Pessoais – LGPD, no âmbito da Administração Pública direta e indireta do Poder Executivo. </t>
   </si>
   <si>
@@ -176,9 +154,6 @@
     <t>GOVERNO DIGITAL </t>
   </si>
   <si>
-    <t>https://www.almg.gov.br/legislacao-mineira/texto/DEC/48383/2022/</t>
-  </si>
-  <si>
     <t>https://www.planalto.gov.br/ccivil_03/_ato2019-2022/2021/lei/l14129.htm</t>
   </si>
   <si>
@@ -194,9 +169,6 @@
     <t>Lei Federal nº 14.133 de 01 de abril de 2021 </t>
   </si>
   <si>
-    <t>https://www.ipsm.mg.gov.br/arquivos/legislacoes/legislacao/leis/lei_14167.pdf</t>
-  </si>
-  <si>
     <t>https://www.planalto.gov.br/ccivil_03/_ato2019-2022/2021/lei/l14133.htm</t>
   </si>
   <si>
@@ -218,9 +190,6 @@
     <t>https://www.planalto.gov.br/ccivil_03/_ato2011-2014/2013/lei/l12846.htm</t>
   </si>
   <si>
-    <t>https://www.almg.gov.br/legislacao-mineira/DEC/46782/2015/</t>
-  </si>
-  <si>
     <t>CADASTRO GERAL DE FORNECEDORES - CAGEF </t>
   </si>
   <si>
@@ -236,9 +205,6 @@
     <t>https://www.almg.gov.br/legislacao-mineira/Dec/45902/2012/</t>
   </si>
   <si>
-    <t>Decreto Estadual nº 46.782 de 23 de junho de 2015</t>
-  </si>
-  <si>
     <t>Lei Estadual nº 13.994 de 18 de setembro de 2001</t>
   </si>
   <si>
@@ -260,37 +226,277 @@
     <t>REPASSES CONSTITUCIONAIS </t>
   </si>
   <si>
-    <t>https://www.planalto.gov.br/ccivil_03/constituicao/constituicao.htm#art158</t>
-  </si>
-  <si>
-    <t>https://www.planalto.gov.br/ccivil_03/constituicao/constituicao.htm#art159</t>
-  </si>
-  <si>
-    <t>https://www.fazenda.mg.gov.br/governo/assuntos_municipais/previsao_repasses/</t>
-  </si>
-  <si>
-    <t>Informações sobre Repasses de Receitas aos Municípios Mineiros disponibilizadas pela Secretaria de Estado de Fazenda. </t>
-  </si>
-  <si>
-    <t>Regras Constitucionais de repasses de IPI da União para os Estados e destes para os Municípios. </t>
-  </si>
-  <si>
-    <t>Regras Constitucionais de repasses de ICMS e IPVA dos Estados para os Municípios. </t>
-  </si>
-  <si>
-    <t>Legislação sobre repasses de ICMS, IPI e IPVA, da União e dos estados, para os municípios </t>
+    <t>Lei Complementar Federal nº 156/2016</t>
+  </si>
+  <si>
+    <t>Altera dispositivos da Lei de Responsabilidade Fiscal.</t>
+  </si>
+  <si>
+    <t>Lei Complementar Federal nº 178/2021</t>
+  </si>
+  <si>
+    <t>Programa de Acompanhamento Fiscal. Impacta demonstrativos e transparência das contas públicas.</t>
+  </si>
+  <si>
+    <t>Estatui normas gerais de direito financeiro para elaboração dos orçamentos e balanços públicos.</t>
+  </si>
+  <si>
+    <t>Consittuição Federal do Brasil</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>Lei</t>
+  </si>
+  <si>
+    <t>Decreto</t>
+  </si>
+  <si>
+    <t>Resolução</t>
+  </si>
+  <si>
+    <t>Portarias</t>
+  </si>
+  <si>
+    <t>Lei Complementar</t>
+  </si>
+  <si>
+    <t>Constituição Federal</t>
+  </si>
+  <si>
+    <t>Constituição Estadual</t>
+  </si>
+  <si>
+    <t>https://www.fazenda.mg.gov.br/governo/assuntos_municipais/previsao_repasses/previsao_repasse_ICMS/portarias_ICMS/</t>
+  </si>
+  <si>
+    <t>Portarias da Superintendência Central de Administração Financeira (SCAF) publicadas no Diário Oficial do Estado, com os valores consolidados por mês, relativas ao exercício atual.</t>
+  </si>
+  <si>
+    <t>Portarias de repasses de ICMS, IPI e IPVA, da União e dos estados, para os municípios </t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/atividade-parlamentar/leis/legislacao-mineira/lei/?tipo=LEI&amp;num=25698&amp;ano=2026&amp;comp=&amp;cons=</t>
+  </si>
+  <si>
+    <t>Lei Estadual nº 25.698 de 14 de janeiro de 2026</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/LEI/25440/2025/</t>
+  </si>
+  <si>
+    <t>Plano Plurianual de Ação Governamental (PPAG) para o quadriênio 2024-2027</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/LEI/24677/2024/</t>
+  </si>
+  <si>
+    <t>Lei Estadual nº 24.677 de 16 de janeiro de 2024</t>
+  </si>
+  <si>
+    <t>CONTABILIDADE PÚBLICA</t>
+  </si>
+  <si>
+    <t>PLANEJAMENTO</t>
+  </si>
+  <si>
+    <t>TRANSPARÊNCIA FISCAL</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/DEC/48821/2024/</t>
+  </si>
+  <si>
+    <t>Decreto Estadual nº 48.821 de 13 de maio de 2024</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/DEC/48383/2022/</t>
+  </si>
+  <si>
+    <t>Decreto Estadual nº 48.237 de 22 de julho de 2021</t>
+  </si>
+  <si>
+    <t>https://www.planalto.gov.br/ccivil_03/_ato2019-2022/2020/decreto/d10540.htm</t>
+  </si>
+  <si>
+    <t>Dispõe sobre o padrão mínimo de qualidade do Sistema Único e Integrado de Execução Orçamentária, Administração Financeira e Controle.</t>
+  </si>
+  <si>
+    <t>Decreto Federal nº 10.540, de 5 de novembro de 2020</t>
+  </si>
+  <si>
+    <t>https://www.planalto.gov.br/ccivil_03/leis/lcp/lcp156.htm</t>
+  </si>
+  <si>
+    <t>https://www.planalto.gov.br/ccivil_03/leis/lcp/lcp178.htm</t>
+  </si>
+  <si>
+    <t>Lei Estadual nº 25.440, de 06 de agosto de 2025</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/texto/LEI/14167/2002/</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/texto/DEC/46644/2014/</t>
+  </si>
+  <si>
+    <t>Dispõe sobre o Código de Conduta Ética do Agente Público e da Alta Administração Estadual.</t>
+  </si>
+  <si>
+    <t>Decreto Estadual nº 46.644, de 06 de novembro de 2014</t>
+  </si>
+  <si>
+    <t>Dispõe sobre as diretrizes para a elaboração e a execução da Lei Orçamentária Anual para o exercício de 2026.</t>
+  </si>
+  <si>
+    <t>Estima as receitas e fixa as despesas do Orçamento Fiscal do Estado e do Orçamento de Investimento das Empresas Controladas pelo Estado para o exercício financeiro de 2026.</t>
+  </si>
+  <si>
+    <t>https://www.planalto.gov.br/ccivil_03/leis/l4320.htm</t>
+  </si>
+  <si>
+    <t>Lei Federal nº 4.320, 17 de março de 1964</t>
+  </si>
+  <si>
+    <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=216861&amp;marc=</t>
+  </si>
+  <si>
+    <t>Aprova a 4ª Edição do Plano Anticorrupção do Poder Executivo do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>ANTICORRUPÇÃO</t>
+  </si>
+  <si>
+    <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=213467&amp;marc=</t>
+  </si>
+  <si>
+    <t>Estabelece o regulamento do Cadastro Geral de Convenentes do Estado de Minas Gerais.</t>
+  </si>
+  <si>
+    <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=213015&amp;marc=</t>
+  </si>
+  <si>
+    <t>Define os procedimentos para a negociação, a celebração e o acompanhamento dos acordos de leniência de que trata a Lei n° 12.846, de 1° de agosto de 2013, no âmbito da Controladoria-Geral do Estado – CGE e da Advocacia-Geral do Estado – AGE.</t>
+  </si>
+  <si>
+    <t>ACORDO DE LENIÊNCIA</t>
+  </si>
+  <si>
+    <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=212145&amp;marc=</t>
+  </si>
+  <si>
+    <t>Altera a Resolução Conjunta CGE/SEPLAG nº 1, de 08 de abril de 2024, que institui a Política de Gestão de Riscos nas Contratações Públicas no âmbito da Administração Pública direta, autárquica e fundacional do Poder Executivo.</t>
+  </si>
+  <si>
+    <t>GESTÃO DE RISCOS</t>
+  </si>
+  <si>
+    <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=209680&amp;marc=</t>
+  </si>
+  <si>
+    <t>Institui a Política de Gestão de Riscos nas Contratações Públicas no âmbito da Administração Pública direta, autárquica e fundacional do Poder Executivo.</t>
+  </si>
+  <si>
+    <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=202421&amp;marc=</t>
+  </si>
+  <si>
+    <t>Dispõe sobre o escopo, o fluxo e os critérios para avaliação objetiva de conflitos de interesses, bem como sobre as responsabilidades e os prazos para sua realização, nos processos relativos ao recebimento de doações de bens móveis e serviços e o recebimento de bens móveis em comodato pela Administração Pública direta, autárquica e fundacional do Poder Executivo.</t>
+  </si>
+  <si>
+    <t>CONFLITO DE INTERESSES</t>
+  </si>
+  <si>
+    <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=183657&amp;marc=</t>
+  </si>
+  <si>
+    <t>PLANO MINEIRO DE INTEGRIDADE</t>
+  </si>
+  <si>
+    <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=168426&amp;marc=</t>
+  </si>
+  <si>
+    <t>Disciplina, no âmbito do Poder Executivo Estadual, a forma de divulgação da remuneração e subsídio recebidos por ocupante de cargo, posto, graduação, função e emprego público, incluindo auxílios, jetons e outras vantagens pecuniárias do pessoal na ativa.</t>
+  </si>
+  <si>
+    <t>Dispõe sobre a atuação conjunta para o fortalecimento do ambiente de integridade no âmbito da Administração Pública estadual nos termos do Decreto Estadual nº 47.185, de 13 de maio de 2017, que estabelece o Plano Mineiro de Promoção da Integridade – PMPI.</t>
+  </si>
+  <si>
+    <t>Resolução Conjunta CGE/AGE Nº 05/2024, 03 de dezembro de 2024</t>
+  </si>
+  <si>
+    <t>Resolução Conjunta CGE/AGE/CBMMG/DER/IPSEMG/OGE/PCMG/ PMMG/SEF/SEGOV/SEJUSP/SEPLAG Nº 01, de 18 de julho de 2025</t>
+  </si>
+  <si>
+    <t>Resolução Conjunta CGE/SEPLAG Nº 01, 8 de abril de 2024</t>
+  </si>
+  <si>
+    <t>Resolução Conjunta CGE/SEPLAG Nº 04, 4 de outubro de 2024</t>
+  </si>
+  <si>
+    <t>Resolução Conjunta SEGOV/CGE/ Nº 02, 30 de dezembro de 2024</t>
+  </si>
+  <si>
+    <t>Resolução Conjunta SEPLAG/CGE Nº 10.668, 3 de novembro de 2022</t>
+  </si>
+  <si>
+    <t>Resolução Conjunta SEPLAG/CGE Nº 8676, de 30 de julho de 2012</t>
+  </si>
+  <si>
+    <t>Resolução Conjunta SEPLAG/CGE Nº 9881/2018, 24 de julho de 2018</t>
+  </si>
+  <si>
+    <t>Consittuição do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/atividade-parlamentar/leis/legislacao-mineira/lei/texto/?tipo=CON&amp;num=1989&amp;ano=1989&amp;comp=&amp;cons=1</t>
+  </si>
+  <si>
+    <t>Constituição do Estado de Minas Gerais de 1989</t>
+  </si>
+  <si>
+    <t>Decreto Federal nº 8.777, 11 de maio de 2016</t>
+  </si>
+  <si>
+    <t>Institui a Política de Dados Abertos do Poder Executivo federal.</t>
+  </si>
+  <si>
+    <t>https://www.planalto.gov.br/ccivil_03/_ato2015-2018/2016/decreto/d8777.htm</t>
+  </si>
+  <si>
+    <t>Decreto Estadual nº 48.419, de 16 de maio de 2022</t>
+  </si>
+  <si>
+    <t>Dispõe sobre a Política Mineira de Promoção da Integridade.</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/legislacao-mineira/DEC/48419/2022/?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=171158</t>
+  </si>
+  <si>
+    <t>Resolução CGE N° 020, 06 de agosto de 2014</t>
+  </si>
+  <si>
+    <t>Estabelece conceitos e diretrizes, no âmbito da Administração direta, autárquica e fundacional do Poder Executivo Estadual, em matéria de dados abertos governamentais.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -314,8 +520,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -649,347 +856,703 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA935541-02A8-4A32-B73D-24181303B3AE}">
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.625" customWidth="1"/>
+    <col min="4" max="4" width="27.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" t="s">
-        <v>76</v>
+      <c r="C40" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1">
+    <sortState ref="A2:E40">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/upload/legislacao.xlsx
+++ b/upload/legislacao.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="103">
   <si>
     <t>TEMA</t>
   </si>
@@ -49,72 +49,27 @@
     <t>LINK</t>
   </si>
   <si>
-    <t>Constituição da República Federativa do Brasil de 1988 </t>
-  </si>
-  <si>
-    <t>https://www.planalto.gov.br/ccivil_03/Constituicao/Constituicao.htm</t>
-  </si>
-  <si>
-    <t>https://www.planalto.gov.br/ccivil_03/leis/LCP/Lcp101.htm</t>
-  </si>
-  <si>
-    <t>https://www.planalto.gov.br/ccivil_03/leis/LCP/Lcp131.htm</t>
-  </si>
-  <si>
-    <t>https://www.planalto.gov.br/ccivil_03/_ato2011-2014/2011/lei/l12527.htm</t>
-  </si>
-  <si>
     <t>https://www.almg.gov.br/legislacao-mineira/DEC/45969/2012/</t>
   </si>
   <si>
     <t>Regulamenta o acesso à informação no âmbito do Poder Executivo Estadual. </t>
   </si>
   <si>
-    <t>Regulamenta o direito constitucional de acesso dos cidadãos às informações públicas e é aplicável aos três Poderes da União, dos Estados, do Distrito Federal e dos Municípios. </t>
-  </si>
-  <si>
-    <t>Acrescenta dispositivos à Lei Complementar nº 101, de 4 de maio de 2000, que estabelece normas de finanças públicas voltadas para a responsabilidade na gestão fiscal e dá outras providências, a fim de determinar a disponibilização, em tempo real, de informações pormenorizadas sobre a execução. </t>
-  </si>
-  <si>
-    <t>Estabelece normas de finanças públicas voltadas para a responsabilidade na gestão fiscal e dá outras providências.</t>
-  </si>
-  <si>
-    <t>Lei Complementar nº 101, de 04 de Maio de 2000 </t>
-  </si>
-  <si>
-    <t>Lei Complementar nº 131, de 27 de Maio de 2009 </t>
-  </si>
-  <si>
-    <t>Lei Federal nº 12.527, de 18 de novembro de 2011 </t>
-  </si>
-  <si>
     <t>Decreto Estadual nº 45.969, de 24 de maio de 2012 </t>
   </si>
   <si>
     <t>TRANSPARÊNCIA PÚBLICA e ACESSO À INFORMAÇÃO </t>
   </si>
   <si>
-    <t>CONSTITUIÇÃO DA REPÚBLICA </t>
-  </si>
-  <si>
     <t>PROTEÇÃO DE DADOS PESSOAIS </t>
   </si>
   <si>
-    <t>Lei Federal nº 13.709, de 14 de agosto de 2018 </t>
-  </si>
-  <si>
     <t>Dispõe sobre a aplicação da Lei Federal nº 13.709, de 14 de agosto de 2018, Lei Geral de Proteção de Dados Pessoais – LGPD, no âmbito da Administração Pública direta e indireta do Poder Executivo. </t>
   </si>
   <si>
-    <t>Lei Geral de Proteção de Dados Pessoais (LGPD). </t>
-  </si>
-  <si>
     <t>LEGISLAÇÃO</t>
   </si>
   <si>
-    <t>https://www.planalto.gov.br/ccivil_03/_ato2015-2018/2018/lei/l13709.htm</t>
-  </si>
-  <si>
     <t>https://www.almg.gov.br/legislacao-mineira/texto/DEC/48237/2021/?cons=1</t>
   </si>
   <si>
@@ -142,54 +97,27 @@
     <t>Regulamenta o Governo Digital Estadual, no âmbito da Administração Pública direta, autárquica e fundacional do Poder Executivo. </t>
   </si>
   <si>
-    <t>Dispõe sobre princípios, regras e instrumentos para o Governo Digital e para o aumento da eficiência pública e altera a Lei nº 7.116, de 29 de agosto de 1983, a Lei nº 12.527, de 18 de novembro de 2011 (Lei de Acesso à Informação), a Lei nº 12.682, de 9 de julho de 2012, e a Lei nº 13.460, de 26 de junho de 2017. </t>
-  </si>
-  <si>
-    <t>Lei Federal nº 14.129, de 29 de março de 2021 </t>
-  </si>
-  <si>
     <t>Decreto Estadual nº 48.383, de 18 de março de 2022</t>
   </si>
   <si>
     <t>GOVERNO DIGITAL </t>
   </si>
   <si>
-    <t>https://www.planalto.gov.br/ccivil_03/_ato2019-2022/2021/lei/l14129.htm</t>
-  </si>
-  <si>
     <t>Dispõe sobre a adoção, no âmbito do Estado, do pregão como modalidade de licitação para a aquisição de bens e serviços comuns e dá outras providências. </t>
   </si>
   <si>
-    <t>Lei de Licitações e Contratos Administrativos. </t>
-  </si>
-  <si>
     <t>Lei Estadual nº 14.167, de 10 de janeiro de 2002</t>
   </si>
   <si>
-    <t>Lei Federal nº 14.133 de 01 de abril de 2021 </t>
-  </si>
-  <si>
-    <t>https://www.planalto.gov.br/ccivil_03/_ato2019-2022/2021/lei/l14133.htm</t>
-  </si>
-  <si>
     <t>LICITAÇÕES E CONTRATOS </t>
   </si>
   <si>
     <t>Dispõe sobre o Processo Administrativo de Responsabilização, previsto na Lei Federal nº 12.846, de 1º de agosto de 2013, no âmbito da Administração Pública do Poder Executivo Estadual. </t>
   </si>
   <si>
-    <t>Dispõe sobre a responsabilização administrativa e civil de pessoas jurídicas pela prática de atos contra a administração pública, nacional ou estrangeira, e dá outras providências. </t>
-  </si>
-  <si>
-    <t>Lei Federal nº 12.846 de 1º de agosto de 2013 </t>
-  </si>
-  <si>
     <t>RESPONSABILIZAÇÃO DE PESSOA JURÍDICA </t>
   </si>
   <si>
-    <t>https://www.planalto.gov.br/ccivil_03/_ato2011-2014/2013/lei/l12846.htm</t>
-  </si>
-  <si>
     <t>CADASTRO GERAL DE FORNECEDORES - CAGEF </t>
   </si>
   <si>
@@ -226,24 +154,6 @@
     <t>REPASSES CONSTITUCIONAIS </t>
   </si>
   <si>
-    <t>Lei Complementar Federal nº 156/2016</t>
-  </si>
-  <si>
-    <t>Altera dispositivos da Lei de Responsabilidade Fiscal.</t>
-  </si>
-  <si>
-    <t>Lei Complementar Federal nº 178/2021</t>
-  </si>
-  <si>
-    <t>Programa de Acompanhamento Fiscal. Impacta demonstrativos e transparência das contas públicas.</t>
-  </si>
-  <si>
-    <t>Estatui normas gerais de direito financeiro para elaboração dos orçamentos e balanços públicos.</t>
-  </si>
-  <si>
-    <t>Consittuição Federal do Brasil</t>
-  </si>
-  <si>
     <t>TIPO</t>
   </si>
   <si>
@@ -259,12 +169,6 @@
     <t>Portarias</t>
   </si>
   <si>
-    <t>Lei Complementar</t>
-  </si>
-  <si>
-    <t>Constituição Federal</t>
-  </si>
-  <si>
     <t>Constituição Estadual</t>
   </si>
   <si>
@@ -295,15 +199,9 @@
     <t>Lei Estadual nº 24.677 de 16 de janeiro de 2024</t>
   </si>
   <si>
-    <t>CONTABILIDADE PÚBLICA</t>
-  </si>
-  <si>
     <t>PLANEJAMENTO</t>
   </si>
   <si>
-    <t>TRANSPARÊNCIA FISCAL</t>
-  </si>
-  <si>
     <t>https://www.almg.gov.br/legislacao-mineira/DEC/48821/2024/</t>
   </si>
   <si>
@@ -316,21 +214,6 @@
     <t>Decreto Estadual nº 48.237 de 22 de julho de 2021</t>
   </si>
   <si>
-    <t>https://www.planalto.gov.br/ccivil_03/_ato2019-2022/2020/decreto/d10540.htm</t>
-  </si>
-  <si>
-    <t>Dispõe sobre o padrão mínimo de qualidade do Sistema Único e Integrado de Execução Orçamentária, Administração Financeira e Controle.</t>
-  </si>
-  <si>
-    <t>Decreto Federal nº 10.540, de 5 de novembro de 2020</t>
-  </si>
-  <si>
-    <t>https://www.planalto.gov.br/ccivil_03/leis/lcp/lcp156.htm</t>
-  </si>
-  <si>
-    <t>https://www.planalto.gov.br/ccivil_03/leis/lcp/lcp178.htm</t>
-  </si>
-  <si>
     <t>Lei Estadual nº 25.440, de 06 de agosto de 2025</t>
   </si>
   <si>
@@ -352,12 +235,6 @@
     <t>Estima as receitas e fixa as despesas do Orçamento Fiscal do Estado e do Orçamento de Investimento das Empresas Controladas pelo Estado para o exercício financeiro de 2026.</t>
   </si>
   <si>
-    <t>https://www.planalto.gov.br/ccivil_03/leis/l4320.htm</t>
-  </si>
-  <si>
-    <t>Lei Federal nº 4.320, 17 de março de 1964</t>
-  </si>
-  <si>
     <t>https://www.pesquisalegislativa.mg.gov.br/LegislacaoCompleta.aspx?cod=216861&amp;marc=</t>
   </si>
   <si>
@@ -452,15 +329,6 @@
   </si>
   <si>
     <t>Constituição do Estado de Minas Gerais de 1989</t>
-  </si>
-  <si>
-    <t>Decreto Federal nº 8.777, 11 de maio de 2016</t>
-  </si>
-  <si>
-    <t>Institui a Política de Dados Abertos do Poder Executivo federal.</t>
-  </si>
-  <si>
-    <t>https://www.planalto.gov.br/ccivil_03/_ato2015-2018/2016/decreto/d8777.htm</t>
   </si>
   <si>
     <t>Decreto Estadual nº 48.419, de 16 de maio de 2022</t>
@@ -857,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
@@ -868,13 +736,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -885,67 +753,67 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>56</v>
@@ -953,129 +821,129 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>131</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>36</v>
@@ -1084,472 +952,251 @@
         <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>145</v>
+        <v>53</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
         <v>44</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35" t="s">
-        <v>100</v>
-      </c>
-      <c r="E35" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" t="s">
-        <v>93</v>
-      </c>
-      <c r="E36" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1">
     <sortState ref="A2:E40">
-      <sortCondition ref="B1"/>
+      <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/upload/legislacao.xlsx
+++ b/upload/legislacao.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="112">
   <si>
     <t>TEMA</t>
   </si>
@@ -347,6 +347,33 @@
   </si>
   <si>
     <t>Estabelece conceitos e diretrizes, no âmbito da Administração direta, autárquica e fundacional do Poder Executivo Estadual, em matéria de dados abertos governamentais.</t>
+  </si>
+  <si>
+    <t>Lei Federal nº 12.527/2011</t>
+  </si>
+  <si>
+    <t>https://www.planalto.gov.br/ccivil_03/_ato2011-2014/2011/lei/l12527.htm</t>
+  </si>
+  <si>
+    <t>Regula o acesso a informações previsto no inciso XXXIII do art. 5º , no inciso II do § 3º do art. 37 e no § 2º do art. 216 da Constituição Federal; altera a Lei nº 8.112, de 11 de dezembro de 1990; revoga a Lei nº 11.111, de 5 de maio de 2005, e dispositivos da Lei nº 8.159, de 8 de janeiro de 1991; e dá outras providências.</t>
+  </si>
+  <si>
+    <t>https://www.planalto.gov.br/ccivil_03/_ato2015-2018/2018/lei/l13709.htm</t>
+  </si>
+  <si>
+    <t>Lei Geral de Proteção de Dados Pessoais (LGPD).</t>
+  </si>
+  <si>
+    <t>Lei Federal nº 13.709/2018</t>
+  </si>
+  <si>
+    <t>https://www.planalto.gov.br/ccivil_03/_ato2019-2022/2021/lei/l14129.htm</t>
+  </si>
+  <si>
+    <t>Lei Federal nº 14.129/2021</t>
+  </si>
+  <si>
+    <t>Dispõe sobre princípios, regras e instrumentos para o Governo Digital e para o aumento da eficiência pública e altera a Lei nº 7.116, de 29 de agosto de 1983, a Lei nº 12.527, de 18 de novembro de 2011 (Lei de Acesso à Informação), a Lei nº 12.682, de 9 de julho de 2012, e a Lei nº 13.460, de 26 de junho de 2017.</t>
   </si>
 </sst>
 </file>
@@ -725,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
@@ -1193,9 +1220,60 @@
         <v>81</v>
       </c>
     </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1">
-    <sortState ref="A2:E40">
+    <sortState ref="A2:E27">
       <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>
